--- a/data/trans_bre/P2A_ner_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2A_ner_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 1,97</t>
+          <t>-1,66; 1,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 1,98</t>
+          <t>-3,64; 1,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 6,82</t>
+          <t>0,03; 6,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 0,37</t>
+          <t>-3,51; 0,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-73,95; 243,88</t>
+          <t>-75,11; 184,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-68,9; 110,18</t>
+          <t>-72,81; 93,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 391,41</t>
+          <t>-5,93; 306,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-71,35; 20,92</t>
+          <t>-71,46; 21,58</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 2,46</t>
+          <t>-2,88; 2,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 4,02</t>
+          <t>-2,46; 3,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 3,93</t>
+          <t>-1,9; 3,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 4,63</t>
+          <t>-0,62; 4,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,39; 112,11</t>
+          <t>-58,2; 118,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-51,28; 145,63</t>
+          <t>-45,71; 145,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,93; 171,2</t>
+          <t>-42,81; 161,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-22,2; 330,19</t>
+          <t>-26,31; 325,12</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 7,84</t>
+          <t>-0,87; 7,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 3,76</t>
+          <t>-1,8; 4,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,71; 15,6</t>
+          <t>3,25; 15,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 5,98</t>
+          <t>-0,36; 6,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-28,87; 356,33</t>
+          <t>-28,28; 350,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-50,05; 155,0</t>
+          <t>-46,58; 186,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52,11; 366,65</t>
+          <t>39,24; 340,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-17,56; 547,34</t>
+          <t>-11,38; 566,87</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 3,38</t>
+          <t>-0,4; 3,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,42</t>
+          <t>0,71; 4,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 6,98</t>
+          <t>1,95; 6,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 56,99</t>
+          <t>0,52; 51,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 130,5</t>
+          <t>-12,57; 132,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,3; 245,35</t>
+          <t>20,41; 225,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,94; 176,92</t>
+          <t>35,59; 183,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,76; 2606,37</t>
+          <t>14,56; 2585,82</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 4,58</t>
+          <t>-0,73; 4,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 5,2</t>
+          <t>0,61; 5,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,96; 14,14</t>
+          <t>7,65; 14,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 2,57</t>
+          <t>-2,26; 2,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,21; 227,33</t>
+          <t>-16,28; 253,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 221,52</t>
+          <t>9,31; 228,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>113,03; 370,07</t>
+          <t>109,63; 363,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-33,54; 76,3</t>
+          <t>-34,89; 79,31</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,37</t>
+          <t>1,72; 5,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,17</t>
+          <t>0,88; 5,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,49; 11,5</t>
+          <t>5,52; 11,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 5,53</t>
+          <t>-0,31; 5,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>50,98; 829,83</t>
+          <t>40,27; 921,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,41; 678,18</t>
+          <t>17,89; 704,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>84,98; 600,31</t>
+          <t>88,55; 607,74</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-27,09; 1267,04</t>
+          <t>-16,36; 1230,18</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,65</t>
+          <t>0,91; 2,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,86</t>
+          <t>0,92; 2,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,3; 7,91</t>
+          <t>5,26; 7,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 23,59</t>
+          <t>1,06; 24,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>21,33; 109,81</t>
+          <t>28,15; 120,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,89; 110,72</t>
+          <t>25,45; 112,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>103,38; 196,08</t>
+          <t>104,08; 197,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>34,82; 795,97</t>
+          <t>31,79; 780,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_ner_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2A_ner_R-Clase-trans_bre.xlsx
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-39,63%</t>
+          <t>-39,16%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,76</t>
+          <t>-1,67; 2,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 1,98</t>
+          <t>-3,27; 1,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 6,38</t>
+          <t>0,32; 6,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 0,37</t>
+          <t>-3,88; 0,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-75,11; 184,28</t>
+          <t>-76,04; 210,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-72,81; 93,09</t>
+          <t>-71,86; 75,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 306,05</t>
+          <t>2,57; 354,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-71,46; 21,58</t>
+          <t>-72,38; 22,58</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,06</t>
+          <t>2,03</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>82,39%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 2,49</t>
+          <t>-2,77; 2,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 3,93</t>
+          <t>-2,85; 3,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 3,92</t>
+          <t>-2,27; 3,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 4,4</t>
+          <t>-0,19; 4,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-58,2; 118,23</t>
+          <t>-58,67; 130,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-45,71; 145,61</t>
+          <t>-52,85; 121,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,81; 161,87</t>
+          <t>-47,84; 189,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-26,31; 325,12</t>
+          <t>-17,23; 313,09</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,29</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 7,55</t>
+          <t>-0,88; 7,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 4,26</t>
+          <t>-1,98; 3,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,25; 15,69</t>
+          <t>2,98; 16,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 6,42</t>
+          <t>-2,11; 4,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-28,28; 350,21</t>
+          <t>-30,98; 316,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-46,58; 186,72</t>
+          <t>-48,74; 140,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39,24; 340,12</t>
+          <t>41,28; 333,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,38; 566,87</t>
+          <t>-42,45; 170,02</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21,08</t>
+          <t>1,3</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>680,81%</t>
+          <t>42,86%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 3,2</t>
+          <t>-0,44; 3,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 4,16</t>
+          <t>0,62; 4,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 6,87</t>
+          <t>2,2; 6,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 51,51</t>
+          <t>-0,21; 2,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,57; 132,46</t>
+          <t>-12,24; 130,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,41; 225,55</t>
+          <t>19,58; 230,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,59; 183,68</t>
+          <t>35,82; 173,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,56; 2585,82</t>
+          <t>-7,38; 118,73</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>1,84</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>42,99%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 4,62</t>
+          <t>-0,64; 4,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,41</t>
+          <t>0,41; 5,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,65; 14,37</t>
+          <t>7,88; 14,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 2,73</t>
+          <t>-0,42; 3,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,28; 253,85</t>
+          <t>-17,38; 254,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,31; 228,64</t>
+          <t>6,38; 237,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>109,63; 363,91</t>
+          <t>115,73; 352,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-34,89; 79,31</t>
+          <t>-8,2; 129,05</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,63</t>
+          <t>3,71</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>209,92%</t>
+          <t>256,78%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,72; 5,58</t>
+          <t>1,5; 5,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,04</t>
+          <t>0,85; 5,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,52; 11,59</t>
+          <t>5,21; 11,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 5,45</t>
+          <t>0,7; 5,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>40,27; 921,93</t>
+          <t>41,35; 854,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,89; 704,48</t>
+          <t>12,49; 729,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>88,55; 607,74</t>
+          <t>80,92; 585,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-16,36; 1230,18</t>
+          <t>-8,04; 1425,96</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,89</t>
+          <t>1,41</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>223,47%</t>
+          <t>42,78%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,81</t>
+          <t>0,97; 2,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,87</t>
+          <t>0,94; 2,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,26; 7,93</t>
+          <t>5,17; 7,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,06; 24,08</t>
+          <t>0,55; 2,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>28,15; 120,37</t>
+          <t>28,87; 115,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,45; 112,23</t>
+          <t>26,95; 105,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>104,08; 197,3</t>
+          <t>101,28; 198,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>31,79; 780,64</t>
+          <t>13,78; 83,2</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_ner_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2A_ner_R-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental</t>
+          <t>Población que convive con personas con problemas de nervios, depresión o trastorno mental</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
